--- a/data/projects/drum-mass/raw/드럼양산평가_샘플.xlsx
+++ b/data/projects/drum-mass/raw/드럼양산평가_샘플.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -526,7 +526,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -551,7 +551,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -576,7 +576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -601,7 +601,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -626,7 +626,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -651,7 +651,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -676,7 +676,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -705,7 +705,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -730,7 +730,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -755,7 +755,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -780,7 +780,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -805,7 +805,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -830,7 +830,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -859,7 +859,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -884,7 +884,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -909,7 +909,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -934,7 +934,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -959,7 +959,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1013,7 +1013,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1063,7 +1063,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1088,7 +1088,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
